--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbelltown Stadium</t>
   </si>
   <si>
     <t xml:space="preserve">17:10</t>
@@ -463,7 +466,7 @@
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="5.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="54.71" hidden="0" customWidth="1"/>
   </cols>
@@ -618,7 +621,9 @@
       <c r="J4" t="s">
         <v>17</v>
       </c>
-      <c r="K4"/>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -657,7 +662,9 @@
       <c r="J5" t="s">
         <v>19</v>
       </c>
-      <c r="K5"/>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -670,13 +677,13 @@
         <v>46277</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
         <v>-7.16212433245236</v>
@@ -709,13 +716,13 @@
         <v>46277</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
         <v>-7.16212433245236</v>
@@ -748,13 +755,13 @@
         <v>46277</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
         <v>-4.40976604263829</v>
@@ -787,13 +794,13 @@
         <v>46277</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
         <v>-4.40976604263829</v>
@@ -826,13 +833,13 @@
         <v>46278</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
         <v>-16.0907688345636</v>
@@ -865,13 +872,13 @@
         <v>46278</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
         <v>-16.0907688345636</v>
@@ -904,13 +911,13 @@
         <v>46278</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>-1.12430166853877</v>
@@ -943,13 +950,13 @@
         <v>46278</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
         <v>-1.12430166853877</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">19:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
     <t xml:space="preserve">FT</t>
@@ -68,6 +68,9 @@
     <t xml:space="preserve">No Rain (Primary)</t>
   </si>
   <si>
+    <t xml:space="preserve">Campbelltown Stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">No - primary model</t>
   </si>
   <si>
@@ -77,49 +80,16 @@
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
   </si>
   <si>
-    <t xml:space="preserve">17:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbelltown Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
+    <t xml:space="preserve">16:05</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">gold coast titans</t>
+    <t xml:space="preserve">Totally Workwear Stadium</t>
   </si>
 </sst>
 </file>
@@ -458,15 +428,15 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="24.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="54.71" hidden="0" customWidth="1"/>
   </cols>
@@ -514,7 +484,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -526,16 +496,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-36.5521715067098</v>
+        <v>9.64718321722199</v>
       </c>
       <c r="F2" t="n">
-        <v>-32.0781818325738</v>
+        <v>11.044926280863</v>
       </c>
       <c r="G2" t="n">
-        <v>-36.5521715067098</v>
+        <v>9.64718321722199</v>
       </c>
       <c r="H2" t="n">
-        <v>57.7750513145418</v>
+        <v>49.0257297891884</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -543,17 +513,19 @@
       <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="K2"/>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -565,55 +537,57 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-36.5521715067098</v>
+        <v>9.64718321722199</v>
       </c>
       <c r="F3" t="n">
-        <v>-32.0781818325738</v>
+        <v>11.044926280863</v>
       </c>
       <c r="G3" t="n">
-        <v>-36.5521715067098</v>
+        <v>9.64718321722199</v>
       </c>
       <c r="H3" t="n">
-        <v>57.7750513145418</v>
+        <v>49.0257297891884</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3"/>
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>9.18387977782106</v>
+        <v>-8.76774996497761</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3637561986678</v>
+        <v>-8.88644848278121</v>
       </c>
       <c r="G4" t="n">
-        <v>9.18387977782106</v>
+        <v>-8.76774996497761</v>
       </c>
       <c r="H4" t="n">
-        <v>51.1992231110232</v>
+        <v>54.0930813776685</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -622,366 +596,54 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>9.18387977782106</v>
+        <v>-8.76774996497761</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3637561986678</v>
+        <v>-8.88644848278121</v>
       </c>
       <c r="G5" t="n">
-        <v>9.18387977782106</v>
+        <v>-8.76774996497761</v>
       </c>
       <c r="H5" t="n">
-        <v>51.1992231110232</v>
+        <v>54.0930813776685</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-7.16212433245236</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-3.7420798264886</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-7.16212433245236</v>
-      </c>
-      <c r="H6" t="n">
-        <v>47.3236763460009</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-7.16212433245236</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-3.7420798264886</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-7.16212433245236</v>
-      </c>
-      <c r="H7" t="n">
-        <v>47.3236763460009</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-4.40976604263829</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-3.47805895338312</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-4.40976604263829</v>
-      </c>
-      <c r="H8" t="n">
-        <v>51.1601385612607</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-4.40976604263829</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-3.47805895338312</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.40976604263829</v>
-      </c>
-      <c r="H9" t="n">
-        <v>51.1601385612607</v>
-      </c>
-      <c r="I9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-16.0907688345636</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-15.6775494166285</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-16.0907688345636</v>
-      </c>
-      <c r="H10" t="n">
-        <v>53.7234972412487</v>
-      </c>
-      <c r="I10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-16.0907688345636</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-15.6775494166285</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-16.0907688345636</v>
-      </c>
-      <c r="H11" t="n">
-        <v>53.7234972412487</v>
-      </c>
-      <c r="I11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1.12430166853877</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.70954831425042</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.12430166853877</v>
-      </c>
-      <c r="H12" t="n">
-        <v>49.0954989732176</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12"/>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.12430166853877</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.70954831425042</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-1.12430166853877</v>
-      </c>
-      <c r="H13" t="n">
-        <v>49.0954989732176</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">wests tigers</t>
+    <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">No Rain (Primary)</t>
   </si>
   <si>
-    <t xml:space="preserve">Campbelltown Stadium</t>
+    <t xml:space="preserve">Allianz Stadium</t>
   </si>
   <si>
     <t xml:space="preserve">No - primary model</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
   </si>
   <si>
-    <t xml:space="preserve">16:05</t>
+    <t xml:space="preserve">13:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totally Workwear Stadium</t>
+    <t xml:space="preserve">Cbus Super Stadium</t>
   </si>
 </sst>
 </file>
@@ -428,15 +428,15 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="24.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="54.71" hidden="0" customWidth="1"/>
   </cols>
@@ -484,7 +484,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46283</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -496,16 +496,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>9.64718321722199</v>
+        <v>-19.2010539079494</v>
       </c>
       <c r="F2" t="n">
-        <v>11.044926280863</v>
+        <v>-17.0756459250955</v>
       </c>
       <c r="G2" t="n">
-        <v>9.64718321722199</v>
+        <v>-19.2010539079494</v>
       </c>
       <c r="H2" t="n">
-        <v>49.0257297891884</v>
+        <v>47.4016607891887</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -517,7 +517,7 @@
         <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46283</v>
+        <v>46291</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -537,16 +537,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>9.64718321722199</v>
+        <v>-19.2010539079494</v>
       </c>
       <c r="F3" t="n">
-        <v>11.044926280863</v>
+        <v>-17.0756459250955</v>
       </c>
       <c r="G3" t="n">
-        <v>9.64718321722199</v>
+        <v>-19.2010539079494</v>
       </c>
       <c r="H3" t="n">
-        <v>49.0257297891884</v>
+        <v>47.5292770374522</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -558,7 +558,7 @@
         <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46284</v>
+        <v>46292</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -578,16 +578,16 @@
         <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.76774996497761</v>
+        <v>7.26118566392989</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.88644848278121</v>
+        <v>5.71380681070824</v>
       </c>
       <c r="G4" t="n">
-        <v>-8.76774996497761</v>
+        <v>7.26118566392989</v>
       </c>
       <c r="H4" t="n">
-        <v>54.0930813776685</v>
+        <v>51.6228882463237</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46284</v>
+        <v>46292</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -619,16 +619,16 @@
         <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.76774996497761</v>
+        <v>7.26118566392989</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.88644848278121</v>
+        <v>5.71380681070824</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.76774996497761</v>
+        <v>7.26118566392989</v>
       </c>
       <c r="H5" t="n">
-        <v>54.0930813776685</v>
+        <v>51.6228882463237</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
+    <t xml:space="preserve">16:00</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">canberra raiders</t>
+    <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
     <t xml:space="preserve">FT</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">No Rain (Primary)</t>
   </si>
   <si>
-    <t xml:space="preserve">Allianz Stadium</t>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
   </si>
   <si>
     <t xml:space="preserve">No - primary model</t>
@@ -78,18 +78,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium</t>
   </si>
 </sst>
 </file>
@@ -428,7 +416,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -436,7 +424,7 @@
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="21.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="54.71" hidden="0" customWidth="1"/>
   </cols>
@@ -484,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46291</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -496,16 +484,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-19.2010539079494</v>
+        <v>-3.86934988323703</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.0756459250955</v>
+        <v>-4.69441407773151</v>
       </c>
       <c r="G2" t="n">
-        <v>-19.2010539079494</v>
+        <v>-3.86934988323703</v>
       </c>
       <c r="H2" t="n">
-        <v>47.4016607891887</v>
+        <v>52.4121857656362</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -517,7 +505,7 @@
         <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -525,7 +513,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46291</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -537,16 +525,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-19.2010539079494</v>
+        <v>-3.86934988323703</v>
       </c>
       <c r="F3" t="n">
-        <v>-17.0756459250955</v>
+        <v>-4.69441407773151</v>
       </c>
       <c r="G3" t="n">
-        <v>-19.2010539079494</v>
+        <v>-3.86934988323703</v>
       </c>
       <c r="H3" t="n">
-        <v>47.5292770374522</v>
+        <v>52.4121857656362</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -558,91 +546,9 @@
         <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.26118566392989</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.71380681070824</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7.26118566392989</v>
-      </c>
-      <c r="H4" t="n">
-        <v>51.6228882463237</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.26118566392989</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.71380681070824</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.26118566392989</v>
-      </c>
-      <c r="H5" t="n">
-        <v>51.6228882463237</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="s">
         <v>21</v>
       </c>
     </row>
